--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15504" yWindow="3432" windowWidth="7536" windowHeight="9072" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sprint" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Historias" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tareas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Criterios de aceptación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Definition of Done" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprint" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historias" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criterios de aceptación" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Definition of Done" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Historias'!$A$5:$P$28</definedName>
@@ -2114,8 +2114,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -2332,7 +2330,7 @@
       <c r="O7" s="11" t="n"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>Base de datos y web terminadas. DECISION PENDIENTE para el criterio 3: pme_activo_medidor es NOT NULL, y un plan sobre cuatro blowers necesita que sea nullable para que cada equipo dispare con su propio horómetro.</t>
+          <t>DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
         </is>
       </c>
     </row>
@@ -2397,13 +2395,17 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="O8" s="7" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O8" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>Plan_Mantenimiento_Ocurrencia.pmo_plan_mantenimiento_hito es NOT NULL contra Plan_Mantenimiento_Hito, que es HU-081 del Sprint 4 y hoy tiene 0 filas: no se puede insertar ninguna ocurrencia. El cálculo de fechas —lo difícil— ya está hecho y probado en FNC_PROGRAMACION_FECHAS (T-3960), y el generador lo reutiliza.</t>
+          <t>Desbloqueada el 12-09-2026 al existir hitos (HU-081). Generador hecho por Bryan (BD/222); falta el job nocturno que lo dispare con @SOLO_AUTOMATICAS=1.</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3553,7 @@
       <c r="O24" s="7" t="n"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>CRUD de condiciones terminado. Bloqueada aguas arriba por HU-041 "Administrar variables de condición", del Sprint 2: Activo_Variable está vacía, así que el combo de la ficha va sin opciones.</t>
+          <t>DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
         </is>
       </c>
     </row>
@@ -5369,8 +5371,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -6231,11 +6231,17 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>La decisión del criterio 3 (pme_activo_medidor NULL, BD/224) permite una programación por medidor sin horómetro fijo; el medidor lo pone cada equipo del plan (pac_activo_medidor).</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="27" customHeight="1" s="19">
       <c r="A25" s="6" t="inlineStr">
@@ -6583,13 +6589,15 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>BD/222 GEN_PLAN_OCURRENCIAS y GEN_TAREA_OCURRENCIAS: XACT_ABORT, idempotentes, con Programacion_Generacion como marca de agua.</t>
         </is>
       </c>
     </row>
@@ -6629,13 +6637,15 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>Reglas en el SP: solo versiones publicadas, programaciones habilitadas, sin duplicar por los dos índices únicos.</t>
         </is>
       </c>
     </row>
@@ -6675,13 +6685,15 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>SEL_PLAN_CALENDARIO (BD/216) devuelve el resultado; el SP de generación devuelve el resumen por plan e hito.</t>
         </is>
       </c>
     </row>
@@ -6721,13 +6733,15 @@
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>_SEMILLA_PLAN_CALENDARIO.sql + generación real sobre PMA-HORNOS-L1.</t>
         </is>
       </c>
     </row>
@@ -6767,13 +6781,15 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>POST /plan-ocurrencias/generar (PlanOcurrenciasController). Probado por HTTP.</t>
         </is>
       </c>
     </row>
@@ -6813,13 +6829,15 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>Los RAISERROR llegan como 400 esDeNegocio (plan sin versión publicada verificado).</t>
         </is>
       </c>
     </row>
@@ -6859,13 +6877,15 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="n">
+        <v>2.25</v>
+      </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>Requiere Plan_Mantenimiento_Hito (HU-081, Sprint 4), hoy con 0 filas.</t>
+          <t>Sin pantalla suelta: botón «Generar ocurrencias» en la pestaña Calendario del plan y en la tarea, con resultado y usuario.</t>
         </is>
       </c>
     </row>
@@ -6905,11 +6925,17 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="n"/>
-      <c r="J39" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>CREAR EDITAR PLANES MANTENIMIENTO en web y API; técnico -&gt; 403 verificado.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="27" customHeight="1" s="19">
       <c r="A40" s="6" t="inlineStr">
@@ -6942,16 +6968,22 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="n"/>
-      <c r="J40" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutados por Bryan (ver S4 y MD): horizonte, repetida sin duplicar, manual, programación deshabilitada.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="27" customHeight="1" s="19">
       <c r="A41" s="6" t="inlineStr">
@@ -6984,16 +7016,22 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="n"/>
-      <c r="J41" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>XML del controlador + MD.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="27" customHeight="1" s="19">
       <c r="A42" s="6" t="inlineStr">
@@ -7026,7 +7064,7 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -7035,7 +7073,11 @@
         </is>
       </c>
       <c r="I42" s="6" t="n"/>
-      <c r="J42" s="7" t="n"/>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente de la PO.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="54.75" customHeight="1" s="19">
       <c r="A43" s="6" t="inlineStr">
@@ -15185,13 +15227,15 @@
       </c>
       <c r="H223" s="6" t="inlineStr">
         <is>
-          <t>Bloqueada</t>
-        </is>
-      </c>
-      <c r="I223" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I223" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J223" s="7" t="inlineStr">
         <is>
-          <t>No se pueden cargar: Activo_Variable esta vacia y su mantenedor es HU-041, del Sprint 2, todavia Por hacer.</t>
+          <t>Desbloqueada al cerrar HU-041 (BD/224). _SEMILLA_PROGRAMACION_CONDICION.sql: una condición (&gt;80 °C, 30 min) y dos con política TODOS.</t>
         </is>
       </c>
     </row>
@@ -21105,7 +21149,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21180,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21211,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21200,7 +21244,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -2260,8 +2260,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
+      <c r="O6" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="69" customHeight="1" s="19">
       <c r="A7" s="9" t="inlineStr">
@@ -3196,11 +3204,19 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O19" s="11" t="n"/>
-      <c r="P19" s="11" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P19" s="11" t="inlineStr">
+        <is>
+          <t>Construida el 16-09-2026 (bloque 236 + RepuestoVidaUtil.aspx). Evidencia S3 con los 3 criterios OK. FALTA la verificacion de los criterios, que es de Catalina.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="69" customHeight="1" s="19">
       <c r="A20" s="6" t="inlineStr">
@@ -3768,11 +3784,19 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O27" s="11" t="n"/>
-      <c r="P27" s="11" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P27" s="11" t="inlineStr">
+        <is>
+          <t>Construida el 16-09-2026 (bloque 236 + ProveedorHistorial.aspx). Evidencia S3 con los 2 criterios OK. FALTA la verificacion de los criterios, que es de Catalina.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="41.25" customHeight="1" s="19">
       <c r="A28" s="6" t="inlineStr">
@@ -4291,7 +4315,7 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Detectores de los otros modulos listos el 16-09-2026 (bloque 238): quedan las pruebas y documentacion de Catalina (T-3958/T-3959).</t>
         </is>
       </c>
     </row>
@@ -5459,11 +5483,15 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Descartada</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
-      <c r="J6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Misma decision que en HU-150: la subida es por recurso con uuid (patron 209), no hay lote que persistir. Sincronizacion_Lote no se crea.</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A7" s="6" t="inlineStr">
@@ -5585,11 +5613,15 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Descartada</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="7" t="n"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Sin tabla de lotes no hay datos que sembrar.</t>
+        </is>
+      </c>
     </row>
     <row r="10" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A10" s="6" t="inlineStr">
@@ -5627,11 +5659,17 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Ya existia como la sabana: GET /sincronizacion (manifiesto) y GET /sincronizacion/{bloque}?desde=, acotada a las plantas del usuario por API_SEL_APP_SABANA_DATOS (bloques 140-234).</t>
+        </is>
+      </c>
     </row>
     <row r="11" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A11" s="6" t="inlineStr">
@@ -5711,11 +5749,17 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>SuscripcionHandler en el pipeline de Web API: con cliente en el token y PUEDE_OPERAR=0 (SEL_SUSCRIPCION_ESTADO_CLIENTE -&gt; FNC_SUSCRIPCION_VIGENTE) responde 402 con el cuerpo estandar; cache 60 s por cliente; registra en Suscripcion_Bloqueo_Log origen API; exentas /sesion, /cliente-usuarios, /mi-perfil.</t>
+        </is>
+      </c>
     </row>
     <row r="13" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A13" s="6" t="inlineStr">
@@ -5879,11 +5923,17 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>La API valida permiso con ExigirPermiso/ExigirCliente y el cliente sale del token, nunca de un parametro; la sabana filtra por las plantas del usuario.</t>
+        </is>
+      </c>
     </row>
     <row r="17" hidden="1" ht="54.75" customHeight="1" s="19">
       <c r="A17" s="6" t="inlineStr">
@@ -12671,11 +12721,17 @@
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I165" s="6" t="n"/>
-      <c r="J165" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J165" s="7" t="inlineStr">
+        <is>
+          <t>Componente_Repuesto_Instalacion ya traia fecha y lectura de instalacion y retiro (nullable): sin cambio de modelo. Indice IX_CRI_CLIENTE_REPUESTO (bloque 108).</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="41.25" customHeight="1" s="19">
       <c r="A166" s="6" t="inlineStr">
@@ -12713,11 +12769,17 @@
       </c>
       <c r="H166" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I166" s="6" t="n"/>
-      <c r="J166" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>SEL_REPUESTO_VIDA_UTIL (bloques 108/236): parametrizado, horas por diferencia de lecturas, dias siempre, promedio/min/max por ventana sobre las cerradas; fechas en hora de Santiago y vida util esperada al lado.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="41.25" customHeight="1" s="19">
       <c r="A167" s="6" t="inlineStr">
@@ -12755,11 +12817,17 @@
       </c>
       <c r="H167" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I167" s="6" t="n"/>
-      <c r="J167" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J167" s="7" t="inlineStr">
+        <is>
+          <t>IX_CRI_CLIENTE_REPUESTO (cliente, repuesto): la columna por la que filtra la pantalla.</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="41.25" customHeight="1" s="19">
       <c r="A168" s="6" t="inlineStr">
@@ -12797,11 +12865,17 @@
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I168" s="6" t="n"/>
-      <c r="J168" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>Bloque 236 sobre el catalogo real (REP-6205 en CMP-33-03 con el horometro MED-33-H): 300 a 8.712 = 8.412 h; 3.388 h; una abierta; una correa sin horometro.</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="27" customHeight="1" s="19">
       <c r="A169" s="6" t="inlineStr">
@@ -12839,11 +12913,17 @@
       </c>
       <c r="H169" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I169" s="6" t="n"/>
-      <c r="J169" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>RepuestoVidaUtil.aspx bajo Inventario &gt; Operacion: tarjetas por repuesto (promedio/min/max vs esperada), filtros repuesto/situacion/texto, grilla y Descargar a Excel.</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="41.25" customHeight="1" s="19">
       <c r="A170" s="6" t="inlineStr">
@@ -12881,11 +12961,17 @@
       </c>
       <c r="H170" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I170" s="6" t="n"/>
-      <c r="J170" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>Menu con VER REPUESTOS (Token.ExigirPagina del master); @CLIENTE de sesion en el controller; la exportacion revalida el permiso en el servidor.</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="41.25" customHeight="1" s="19">
       <c r="A171" s="6" t="inlineStr">
@@ -16699,11 +16785,17 @@
       </c>
       <c r="H255" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I255" s="6" t="n"/>
-      <c r="J255" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I255" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J255" s="7" t="inlineStr">
+        <is>
+          <t>Orden_Trabajo_Servicio no tiene cliente: se filtra por la orden Y por el proveedor. Sin codigo propio (es una linea). Indice IX_OTS_PROVEEDOR (bloque 108).</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="27" customHeight="1" s="19">
       <c r="A256" s="6" t="inlineStr">
@@ -16741,11 +16833,17 @@
       </c>
       <c r="H256" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I256" s="6" t="n"/>
-      <c r="J256" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I256" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>SEL_PROVEEDOR_HISTORIAL (bloques 108/236): parametrizado, total por moneda por ventana, ordenes distintas; el rango de fechas ahora entra antes de contar (defecto del 108 corregido).</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="27" customHeight="1" s="19">
       <c r="A257" s="6" t="inlineStr">
@@ -16783,11 +16881,17 @@
       </c>
       <c r="H257" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I257" s="6" t="n"/>
-      <c r="J257" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I257" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>IX_OTS_PROVEEDOR sobre ots_proveedor.</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="27" customHeight="1" s="19">
       <c r="A258" s="6" t="inlineStr">
@@ -16825,11 +16929,17 @@
       </c>
       <c r="H258" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I258" s="6" t="n"/>
-      <c r="J258" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I258" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>Bloque 236 sobre ordenes cerradas reales: Frio Sur 450.000 + 280.000 CLP, 12,5 UF y uno sin moneda; RodPac 150.000 CLP.</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="54.75" customHeight="1" s="19">
       <c r="A259" s="6" t="inlineStr">
@@ -16867,11 +16977,17 @@
       </c>
       <c r="H259" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I259" s="6" t="n"/>
-      <c r="J259" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I259" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J259" s="7" t="inlineStr">
+        <is>
+          <t>ProveedorHistorial.aspx bajo Terceros &gt; Proveedores: tarjetas por moneda + ordenes, filtros proveedor/tipo/rango/texto, grilla, Descargar a Excel; enlace desde el maestro de proveedores.</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="41.25" customHeight="1" s="19">
       <c r="A260" s="6" t="inlineStr">
@@ -16909,11 +17025,17 @@
       </c>
       <c r="H260" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I260" s="6" t="n"/>
-      <c r="J260" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I260" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J260" s="7" t="inlineStr">
+        <is>
+          <t>Menu con VER PROVEEDORES; @CLIENTE de sesion por los dos caminos; exportacion revalida el permiso.</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="41.25" customHeight="1" s="19">
       <c r="A261" s="6" t="inlineStr">
@@ -19479,11 +19601,17 @@
       </c>
       <c r="H321" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I321" s="6" t="n"/>
-      <c r="J321" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I321" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J321" s="7" t="inlineStr">
+        <is>
+          <t>GEN_ALERTA_OPERACION (bloque 238): ocurrencia vencida sin OT, permiso vencido, variable sin medicion en su frecuencia, hallazgo alto/critico sin OT, descubrimientos de terreno sin revisar, medidor proximo al disparo del plan. Alerta gana ale_permiso_trabajo, ale_activo_variable y ale_checklist_hallazgo. GEN_ALERTA_DETECTAR corre los dos detectores.</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="41.25" customHeight="1" s="19">
       <c r="A322" s="6" t="inlineStr">
@@ -22037,7 +22165,7 @@
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22069,7 +22197,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22228,7 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22669,7 +22797,7 @@
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22701,7 +22829,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -2257,7 +2257,7 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
         </is>
       </c>
     </row>
@@ -5483,13 +5483,13 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Descartada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Misma decision que en HU-150: la subida es por recurso con uuid (patron 209), no hay lote que persistir. Sincronizacion_Lote no se crea.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Descartada. Misma decision que en HU-150: la subida es por recurso con uuid (patron 209), no hay lote que persistir. Sincronizacion_Lote no se crea.</t>
         </is>
       </c>
     </row>
@@ -5529,11 +5529,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
-      <c r="J7" s="7" t="n"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1" ht="41.25" customHeight="1" s="19">
       <c r="A8" s="6" t="inlineStr">
@@ -5571,11 +5575,15 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="7" t="n"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="9" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A9" s="6" t="inlineStr">
@@ -5613,13 +5621,13 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>Descartada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Sin tabla de lotes no hay datos que sembrar.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Descartada. Sin tabla de lotes no hay datos que sembrar.</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5667,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I10" s="6" t="n">
@@ -5667,7 +5675,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Ya existia como la sabana: GET /sincronizacion (manifiesto) y GET /sincronizacion/{bloque}?desde=, acotada a las plantas del usuario por API_SEL_APP_SABANA_DATOS (bloques 140-234).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. Ya existia como la sabana: GET /sincronizacion (manifiesto) y GET /sincronizacion/{bloque}?desde=, acotada a las plantas del usuario por API_SEL_APP_SABANA_DATOS (bloques 140-234).</t>
         </is>
       </c>
     </row>
@@ -5707,11 +5715,15 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="7" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="12" hidden="1" ht="41.25" customHeight="1" s="19">
       <c r="A12" s="6" t="inlineStr">
@@ -5749,7 +5761,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I12" s="6" t="n">
@@ -5757,7 +5769,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>SuscripcionHandler en el pipeline de Web API: con cliente en el token y PUEDE_OPERAR=0 (SEL_SUSCRIPCION_ESTADO_CLIENTE -&gt; FNC_SUSCRIPCION_VIGENTE) responde 402 con el cuerpo estandar; cache 60 s por cliente; registra en Suscripcion_Bloqueo_Log origen API; exentas /sesion, /cliente-usuarios, /mi-perfil.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. SuscripcionHandler en el pipeline de Web API: con cliente en el token y PUEDE_OPERAR=0 (SEL_SUSCRIPCION_ESTADO_CLIENTE -&gt; FNC_SUSCRIPCION_VIGENTE) responde 402 con el cuerpo estandar; cache 60 s por cliente; registra en Suscripcion_Bloqueo_Log origen API; exentas /sesion, /cliente-usuarios, /mi-perfil.</t>
         </is>
       </c>
     </row>
@@ -5797,11 +5809,15 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="7" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="14" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A14" s="6" t="inlineStr">
@@ -5839,11 +5855,15 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="7" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="15" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A15" s="6" t="inlineStr">
@@ -5881,11 +5901,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="7" t="n"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="16" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A16" s="6" t="inlineStr">
@@ -5923,7 +5947,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I16" s="6" t="n">
@@ -5931,7 +5955,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>La API valida permiso con ExigirPermiso/ExigirCliente y el cliente sale del token, nunca de un parametro; la sabana filtra por las plantas del usuario.</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Terminada. La API valida permiso con ExigirPermiso/ExigirCliente y el cliente sale del token, nunca de un parametro; la sabana filtra por las plantas del usuario.</t>
         </is>
       </c>
     </row>
@@ -5971,11 +5995,15 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="7" t="n"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="18" hidden="1" ht="41.25" customHeight="1" s="19">
       <c r="A18" s="6" t="inlineStr">
@@ -6013,11 +6041,15 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="7" t="n"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="19" hidden="1" ht="41.25" customHeight="1" s="19">
       <c r="A19" s="6" t="inlineStr">
@@ -6055,11 +6087,15 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="7" t="n"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27" customHeight="1" s="19">
       <c r="A20" s="6" t="inlineStr">
@@ -8703,11 +8739,15 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I76" s="6" t="n"/>
-      <c r="J76" s="7" t="n"/>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="41.25" customHeight="1" s="19">
       <c r="A77" s="6" t="inlineStr">
@@ -9777,11 +9817,15 @@
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I99" s="6" t="n"/>
-      <c r="J99" s="7" t="n"/>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="27" customHeight="1" s="19">
       <c r="A100" s="6" t="inlineStr">
@@ -10975,11 +11019,15 @@
       </c>
       <c r="H125" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I125" s="6" t="n"/>
-      <c r="J125" s="7" t="n"/>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="41.25" customHeight="1" s="19">
       <c r="A126" s="6" t="inlineStr">
@@ -14057,11 +14105,15 @@
       </c>
       <c r="H195" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I195" s="6" t="n"/>
-      <c r="J195" s="7" t="n"/>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="41.25" customHeight="1" s="19">
       <c r="A196" s="6" t="inlineStr">
@@ -16195,13 +16247,13 @@
       </c>
       <c r="H242" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I242" s="6" t="n"/>
       <c r="J242" s="7" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -17577,13 +17629,13 @@
       </c>
       <c r="H273" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I273" s="6" t="n"/>
       <c r="J273" s="7" t="inlineStr">
         <is>
-          <t>Nace de la correccion de alcance de la app (30-08-2026).</t>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer. Nace de la correccion de alcance de la app (30-08-2026).</t>
         </is>
       </c>
     </row>
@@ -18631,11 +18683,15 @@
       </c>
       <c r="H298" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>Movida a Sprint 6</t>
         </is>
       </c>
       <c r="I298" s="6" t="n"/>
-      <c r="J298" s="7" t="n"/>
+      <c r="J298" s="7" t="inlineStr">
+        <is>
+          <t>Movida al Sprint 6 (Sprint Review 1, 15-09-2026). Estado al moverla: Por hacer.</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="41.25" customHeight="1" s="19">
       <c r="A299" s="6" t="inlineStr">

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -2335,10 +2335,14 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="O7" s="11" t="n"/>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
+          <t>Pruebas S3 (17-09): #3 OK (medidor por equipo). #1/#2 NO: el disparo por lectura no está construido (pendiente §10.9). DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
         </is>
       </c>
     </row>
@@ -2481,10 +2485,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O9" s="11" t="n"/>
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Base de datos y web terminadas. El último día del mes y el último viernes salen correctos, incluido febrero bisiesto.</t>
+          <t>Pruebas S3 (17-09): 3 criterios OK (martes/jueves, último día del mes con bisiesto, último viernes). Base de datos y web terminadas. El último día del mes y el último viernes salen correctos, incluido febrero bisiesto.</t>
         </is>
       </c>
     </row>
@@ -2852,10 +2860,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O14" s="7" t="n"/>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>Base de datos y web terminadas. Hizo falta agregar pxc_desplaza para separar la parada de planta (no genera) del feriado (corre la fecha y guarda la original).</t>
+          <t>Pruebas S3 (17-09): 3 criterios OK (ventana, feriado desplazado con fecha original, parada de planta). Base de datos y web terminadas. Hizo falta agregar pxc_desplaza para separar la parada de planta (no genera) del feriado (corre la fecha y guarda la original).</t>
         </is>
       </c>
     </row>
@@ -2995,11 +3007,19 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>Construida por Bryan (bloque 91). Pruebas S3 (17-09): 2 criterios OK.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="54.75" customHeight="1" s="19">
       <c r="A17" s="9" t="inlineStr">
@@ -3062,11 +3082,19 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O17" s="11" t="n"/>
-      <c r="P17" s="11" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O17" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P17" s="11" t="inlineStr">
+        <is>
+          <t>Construida por Bryan (bloque 92). Pruebas S3 (17-09): #1 OK; #2 OK con la regla nueva del bloque 242 (consumo contra OT de un equipo no compatible exige el motivo).</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="54.75" customHeight="1" s="19">
       <c r="A18" s="6" t="inlineStr">
@@ -3289,7 +3317,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>Construida por Emilio Fuentes (01-09-2026). La BD ya estaba (bloque 101: SEL/INS/UPD/DEL_PROCEDIMIENTO y SEL_VARIABLE_MEDICION); revisada y confirmada. AGREGADO: datos de prueba (bloque 130), pantallas en Mantenimiento → Procedimientos (listado + ficha, patrón SigmaModal, ficha rediseñada estilo Programaciones) y permisos/menú (bloque 131). El código no es automático a propósito: la llave es (cliente, código, versión). Compila exitcode=0. PENDIENTE: prueba en navegador (verificación de criterios, de Catalina).</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK; la OT generada copia los pasos del procedimiento (bloque 241). Construida por Emilio Fuentes (01-09-2026). La BD ya estaba (bloque 101: SEL/INS/UPD/DEL_PROCEDIMIENTO y SEL_VARIABLE_MEDICION); revisada y confirmada. AGREGADO: datos de prueba (bloque 130), pantallas en Mantenimiento → Procedimientos (listado + ficha, patrón SigmaModal, ficha rediseñada estilo Programaciones) y permisos/menú (bloque 131). El código no es automático a propósito: la llave es (cliente, código, versión). Compila exitcode=0. PENDIENTE: prueba en navegador (verificación de criterios, de Catalina).</t>
         </is>
       </c>
     </row>
@@ -3354,11 +3382,19 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="n"/>
-      <c r="P21" s="11" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P21" s="11" t="inlineStr">
+        <is>
+          <t>Construida por Bryan (bloque 94). Pruebas S3 (17-09): #1 y #2 OK (el documento firmado es obligatorio para autorizar; la subida depende de la API de archivos del Sprint 6); #3 OK con la regla nueva del bloque 242 (tomar la OT con el permiso vencido se rechaza).</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="82.5" customHeight="1" s="19">
       <c r="A22" s="6" t="inlineStr">
@@ -3424,10 +3460,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O22" s="7" t="n"/>
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Base de datos y web terminadas. Los criterios se pueden ejercitar con la vista previa de fechas de la ficha.</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK sobre FNC_PROGRAMACION_FECHAS y la ficha. Base de datos y web terminadas. Los criterios se pueden ejercitar con la vista previa de fechas de la ficha.</t>
         </is>
       </c>
     </row>
@@ -3495,10 +3535,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O23" s="11" t="n"/>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>Base de datos y web terminadas. Hizo falta agregar pin_desde_ejecucion: sin esa columna los dos criterios de la historia se contradicen.</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK. Base de datos y web terminadas. Hizo falta agregar pin_desde_ejecucion: sin esa columna los dos criterios de la historia se contradicen.</t>
         </is>
       </c>
     </row>
@@ -3566,10 +3610,14 @@
           <t>En curso</t>
         </is>
       </c>
-      <c r="O24" s="7" t="n"/>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
+          <t>Pruebas S3 (17-09): #1-#3 NO: las condiciones se definen pero el disparo al registrar la medición no está construido (pendiente §10.9). DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3767,7 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil.</t>
+          <t>Pruebas S3 (17-09): #1 OK (bloque 241: un paso de OT por cada paso del procedimiento); #2 y #3 quedan definidos en la web y su exigencia al ejecutar es de la app (Sprint 6). Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil.</t>
         </is>
       </c>
     </row>
@@ -3859,13 +3907,17 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O28" s="7" t="n"/>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): Web → Web y App. Promovida a App: el prevencionista verifica el permiso en el frente de trabajo.</t>
+          <t>Construida por Bryan (bloque 97). Pruebas S3 (17-09): 2 criterios OK. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el prevencionista verifica el permiso en el frente de trabajo.</t>
         </is>
       </c>
     </row>
@@ -6503,11 +6555,17 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="27" customHeight="1" s="19">
       <c r="A29" s="6" t="inlineStr">
@@ -7569,11 +7627,17 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="n"/>
-      <c r="J51" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="41.25" customHeight="1" s="19">
       <c r="A52" s="6" t="inlineStr">
@@ -8175,11 +8239,17 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I64" s="6" t="n"/>
-      <c r="J64" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="41.25" customHeight="1" s="19">
       <c r="A65" s="6" t="inlineStr">
@@ -8833,11 +8903,17 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="n"/>
-      <c r="J78" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="27" customHeight="1" s="19">
       <c r="A79" s="6" t="inlineStr">
@@ -9397,11 +9473,17 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="n"/>
-      <c r="J90" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="27" customHeight="1" s="19">
       <c r="A91" s="6" t="inlineStr">
@@ -9911,11 +9993,17 @@
       </c>
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="n"/>
-      <c r="J101" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="27" customHeight="1" s="19">
       <c r="A102" s="6" t="inlineStr">
@@ -10455,11 +10543,17 @@
       </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I113" s="6" t="n"/>
-      <c r="J113" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="41.25" customHeight="1" s="19">
       <c r="A114" s="6" t="inlineStr">
@@ -11113,11 +11207,17 @@
       </c>
       <c r="H127" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I127" s="6" t="n"/>
-      <c r="J127" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="27" customHeight="1" s="19">
       <c r="A128" s="6" t="inlineStr">
@@ -11617,11 +11717,17 @@
       </c>
       <c r="H139" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I139" s="6" t="n"/>
-      <c r="J139" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="27" customHeight="1" s="19">
       <c r="A140" s="6" t="inlineStr">
@@ -12121,11 +12227,17 @@
       </c>
       <c r="H151" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="27" customHeight="1" s="19">
       <c r="A152" s="6" t="inlineStr">
@@ -12685,11 +12797,17 @@
       </c>
       <c r="H163" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I163" s="6" t="n"/>
-      <c r="J163" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="41.25" customHeight="1" s="19">
       <c r="A164" s="6" t="inlineStr">
@@ -13057,11 +13175,17 @@
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I171" s="6" t="n"/>
-      <c r="J171" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="41.25" customHeight="1" s="19">
       <c r="A172" s="6" t="inlineStr">
@@ -13601,11 +13725,17 @@
       </c>
       <c r="H183" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I183" s="6" t="n"/>
-      <c r="J183" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J183" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="184" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A184" s="6" t="inlineStr">
@@ -14193,11 +14323,17 @@
       </c>
       <c r="H197" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I197" s="6" t="n"/>
-      <c r="J197" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I197" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="27" customHeight="1" s="19">
       <c r="A198" s="6" t="inlineStr">
@@ -14645,11 +14781,17 @@
       </c>
       <c r="H207" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I207" s="6" t="n"/>
-      <c r="J207" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="41.25" customHeight="1" s="19">
       <c r="A208" s="6" t="inlineStr">
@@ -15097,11 +15239,17 @@
       </c>
       <c r="H217" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I217" s="6" t="n"/>
-      <c r="J217" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I217" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J217" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="27" customHeight="1" s="19">
       <c r="A218" s="6" t="inlineStr">
@@ -15551,11 +15699,17 @@
       </c>
       <c r="H227" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I227" s="6" t="n"/>
-      <c r="J227" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I227" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J227" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="27" customHeight="1" s="19">
       <c r="A228" s="6" t="inlineStr">
@@ -16163,11 +16317,17 @@
       </c>
       <c r="H240" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I240" s="6" t="n"/>
-      <c r="J240" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I240" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J240" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="27" customHeight="1" s="19">
       <c r="A241" s="6" t="inlineStr">
@@ -16753,11 +16913,17 @@
       </c>
       <c r="H253" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I253" s="6" t="n"/>
-      <c r="J253" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I253" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J253" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="254" hidden="1" ht="41.25" customHeight="1" s="19">
       <c r="A254" s="6" t="inlineStr">
@@ -17125,11 +17291,17 @@
       </c>
       <c r="H261" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I261" s="6" t="n"/>
-      <c r="J261" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I261" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="27" customHeight="1" s="19">
       <c r="A262" s="6" t="inlineStr">
@@ -17545,11 +17717,17 @@
       </c>
       <c r="H271" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I271" s="6" t="n"/>
-      <c r="J271" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I271" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J271" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="54.75" customHeight="1" s="19">
       <c r="A272" s="6" t="inlineStr">
@@ -19705,11 +19883,17 @@
       </c>
       <c r="H322" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I322" s="6" t="n"/>
-      <c r="J322" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I322" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J322" s="7" t="inlineStr">
+        <is>
+          <t>Ejecutadas por Bryan Chávez el 17-09-2026 con evidencia por criterio (Informe de Pruebas Sprint 3, capturas/S3).</t>
+        </is>
+      </c>
     </row>
     <row r="323" ht="41.25" customHeight="1" s="19">
       <c r="A323" s="6" t="inlineStr">
@@ -21301,7 +21485,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21459,7 +21643,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21491,7 +21675,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21706,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21872,7 +22056,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21904,7 +22088,7 @@
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21935,7 +22119,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22216,7 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22064,7 +22248,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22095,7 +22279,7 @@
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22310,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22315,7 +22499,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22347,7 +22531,7 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22379,7 +22563,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22410,7 +22594,7 @@
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22626,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22505,7 +22689,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22537,7 +22721,7 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22752,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22758,7 +22942,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22917,7 +23101,7 @@
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22948,7 +23132,7 @@
       </c>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -2252,7 +2252,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A6,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A6,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -2327,12 +2327,12 @@
         <v>3</v>
       </c>
       <c r="M7" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A7,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A7,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): #3 OK (medidor por equipo). #1/#2 NO: el disparo por lectura no está construido (pendiente §10.9). DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
+          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #3 OK (medidor por equipo). #1/#2 NO: el disparo por lectura no está construido (pendiente §10.9). DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A8,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A8,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N8" s="6" t="inlineStr">
@@ -2477,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A9,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A9,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N9" s="9" t="inlineStr">
@@ -2552,7 +2552,7 @@
         <v>3</v>
       </c>
       <c r="M10" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A10,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A10,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N10" s="6" t="inlineStr">
@@ -2627,7 +2627,7 @@
         <v>3</v>
       </c>
       <c r="M11" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A11,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A11,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N11" s="9" t="inlineStr">
@@ -2702,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="M12" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A12,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A12,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N12" s="6" t="inlineStr">
@@ -2777,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="M13" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A13,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A13,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N13" s="9" t="inlineStr">
@@ -2852,7 +2852,7 @@
         <v>3</v>
       </c>
       <c r="M14" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A14,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A14,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N14" s="6" t="inlineStr">
@@ -2927,7 +2927,7 @@
         <v>2</v>
       </c>
       <c r="M15" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A15,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A15,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N15" s="9" t="inlineStr">
@@ -3002,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="M16" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A16,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A16,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -3077,7 +3077,7 @@
         <v>2</v>
       </c>
       <c r="M17" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A17,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A17,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N17" s="9" t="inlineStr">
@@ -3152,7 +3152,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A18,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A18,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N18" s="6" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A19,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A19,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N19" s="9" t="inlineStr">
@@ -3302,7 +3302,7 @@
         <v>2</v>
       </c>
       <c r="M20" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A20,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A20,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -3377,7 +3377,7 @@
         <v>3</v>
       </c>
       <c r="M21" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A21,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A21,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N21" s="9" t="inlineStr">
@@ -3452,7 +3452,7 @@
         <v>2</v>
       </c>
       <c r="M22" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A22,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A22,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N22" s="6" t="inlineStr">
@@ -3527,7 +3527,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A23,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A23,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N23" s="9" t="inlineStr">
@@ -3602,12 +3602,12 @@
         <v>3</v>
       </c>
       <c r="M24" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A24,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A24,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): #1-#3 NO: las condiciones se definen pero el disparo al registrar la medición no está construido (pendiente §10.9). DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
+          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #1-#3 NO: las condiciones se definen pero el disparo al registrar la medición no está construido (pendiente §10.9). DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3677,7 @@
         <v>2</v>
       </c>
       <c r="M25" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A25,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A25,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N25" s="9" t="inlineStr">
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
       <c r="M26" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A26,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A26,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): #1 OK (bloque 241: un paso de OT por cada paso del procedimiento); #2 y #3 quedan definidos en la web y su exigencia al ejecutar es de la app (Sprint 6). Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil.</t>
+          <t>Bryan (17-09-2026): el servidor exige la medición y respeta el punto de control al completar el paso (bloque 244); #2 y #3 OK por API. Pruebas S3 (17-09): #1 OK (bloque 241: un paso de OT por cada paso del procedimiento); #2 y #3 quedan definidos en la web y su exigencia al ejecutar es de la app (Sprint 6). Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil.</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
         <v>2</v>
       </c>
       <c r="M27" s="9">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A27,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A27,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N27" s="9" t="inlineStr">
@@ -3902,7 +3902,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A28,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A28,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N28" s="6" t="inlineStr">
@@ -3977,7 +3977,7 @@
         <v>4</v>
       </c>
       <c r="M29" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A29,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A29,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -4052,7 +4052,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A30,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A30,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N30" s="6" t="inlineStr">
@@ -4127,7 +4127,7 @@
         <v>3</v>
       </c>
       <c r="M31" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A31,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A31,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N31" s="6" t="inlineStr">
@@ -4202,7 +4202,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A32,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A32,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N32" s="6" t="inlineStr">
@@ -4277,7 +4277,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A33,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A33,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N33" s="6" t="inlineStr">
@@ -4352,7 +4352,7 @@
         <v>4</v>
       </c>
       <c r="M34" s="6">
-        <f>SUMIF(Tareas!$B$6:$B$335,$A34,Tareas!$F$6:$F$335)</f>
+        <f>SUMIF(Tareas!$B$6:$B$341,$A34,Tareas!$F$6:$F$341)</f>
         <v/>
       </c>
       <c r="N34" s="6" t="inlineStr">
@@ -5417,7 +5417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J335"/>
+  <dimension ref="A1:J341"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.7109375" customWidth="1" style="19" min="1" max="1"/>
@@ -20489,12 +20489,294 @@
       </c>
       <c r="J335" s="7" t="n"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1" s="19"/>
-    <row r="337" ht="15.75" customHeight="1" s="19"/>
-    <row r="338" ht="15.75" customHeight="1" s="19"/>
-    <row r="339" ht="15.75" customHeight="1" s="19"/>
-    <row r="340" ht="15.75" customHeight="1" s="19"/>
-    <row r="341" ht="15.75" customHeight="1" s="19"/>
+    <row r="336" ht="15.75" customHeight="1" s="19">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t>T-3972</t>
+        </is>
+      </c>
+      <c r="B336" s="6" t="inlineStr">
+        <is>
+          <t>HU-073</t>
+        </is>
+      </c>
+      <c r="C336" s="7" t="inlineStr">
+        <is>
+          <t>Crear una programación por medidor</t>
+        </is>
+      </c>
+      <c r="D336" s="10" t="inlineStr">
+        <is>
+          <t>FNC_PLAN_MEDIDOR_ESTADO + GEN_PLAN_OCURRENCIAS_MEDIDOR (bloque 243): el horómetro de cada equipo del plan, próximo valor desde la última ocurrencia, ocurrencia al alcanzarlo (#1/#3) y alerta de aviso sin OT dentro de la anticipación (#2).</t>
+        </is>
+      </c>
+      <c r="E336" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F336" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G336" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I336" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J336" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="15.75" customHeight="1" s="19">
+      <c r="A337" s="6" t="inlineStr">
+        <is>
+          <t>T-3973</t>
+        </is>
+      </c>
+      <c r="B337" s="6" t="inlineStr">
+        <is>
+          <t>HU-073</t>
+        </is>
+      </c>
+      <c r="C337" s="7" t="inlineStr">
+        <is>
+          <t>Crear una programación por medidor</t>
+        </is>
+      </c>
+      <c r="D337" s="10" t="inlineStr">
+        <is>
+          <t>API_INS_ACTIVO_MEDIDOR_LECTURA llama al generador tras el commit; UPS_PROGRAMACION_MEDIDOR acepta medidor vacío (= el de cada equipo); GEN_ALERTA_OPERACION comparte la vista.</t>
+        </is>
+      </c>
+      <c r="E337" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F337" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G337" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H337" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I337" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J337" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="15.75" customHeight="1" s="19">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>T-3974</t>
+        </is>
+      </c>
+      <c r="B338" s="6" t="inlineStr">
+        <is>
+          <t>HU-074</t>
+        </is>
+      </c>
+      <c r="C338" s="7" t="inlineStr">
+        <is>
+          <t>Crear una programación por condición</t>
+        </is>
+      </c>
+      <c r="D338" s="10" t="inlineStr">
+        <is>
+          <t>GEN_PLAN_OCURRENCIAS_CONDICION (bloque 243): evalúa las condiciones sobre la última medición en la unidad de la variable, duración mínima por racha (#2) y política TODOS/UNO (#3); una ocurrencia viva por hito y equipo.</t>
+        </is>
+      </c>
+      <c r="E338" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F338" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G338" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H338" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I338" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J338" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="15.75" customHeight="1" s="19">
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>T-3975</t>
+        </is>
+      </c>
+      <c r="B339" s="6" t="inlineStr">
+        <is>
+          <t>HU-074</t>
+        </is>
+      </c>
+      <c r="C339" s="7" t="inlineStr">
+        <is>
+          <t>Crear una programación por condición</t>
+        </is>
+      </c>
+      <c r="D339" s="10" t="inlineStr">
+        <is>
+          <t>API_INS_ACTIVO_MEDICION llama al generador tras el commit, con su propio TRY para no perder la medición.</t>
+        </is>
+      </c>
+      <c r="E339" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F339" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G339" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I339" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J339" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="15.75" customHeight="1" s="19">
+      <c r="A340" s="6" t="inlineStr">
+        <is>
+          <t>T-3976</t>
+        </is>
+      </c>
+      <c r="B340" s="6" t="inlineStr">
+        <is>
+          <t>HU-062</t>
+        </is>
+      </c>
+      <c r="C340" s="7" t="inlineStr">
+        <is>
+          <t>Definir los pasos de un procedimiento</t>
+        </is>
+      </c>
+      <c r="D340" s="10" t="inlineStr">
+        <is>
+          <t>API_UPD_ORDEN_TRABAJO_PASO (bloque 244): un paso que exige medición no se completa sin el valor y lo registra en Activo_Medicion con la OT como origen (#2); un punto de control pendiente bloquea los pasos siguientes (#3).</t>
+        </is>
+      </c>
+      <c r="E340" s="6" t="inlineStr">
+        <is>
+          <t>Base de datos</t>
+        </is>
+      </c>
+      <c r="F340" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G340" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I340" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J340" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="15.75" customHeight="1" s="19">
+      <c r="A341" s="6" t="inlineStr">
+        <is>
+          <t>T-3977</t>
+        </is>
+      </c>
+      <c r="B341" s="6" t="inlineStr">
+        <is>
+          <t>HU-062</t>
+        </is>
+      </c>
+      <c r="C341" s="7" t="inlineStr">
+        <is>
+          <t>Definir los pasos de un procedimiento</t>
+        </is>
+      </c>
+      <c r="D341" s="10" t="inlineStr">
+        <is>
+          <t>PasoResultadoDto gana valor_medicion y unidad_medida; el controller los pasa al SP. Compila 0 errores.</t>
+        </is>
+      </c>
+      <c r="E341" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="F341" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G341" s="7" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="inlineStr">
+        <is>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I341" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J341" s="7" t="inlineStr">
+        <is>
+          <t>Construido y probado el 17-09-2026 (evidencia S3 por criterio). Tomado por Bryan a pedido suyo.</t>
+        </is>
+      </c>
+    </row>
     <row r="342" ht="15.75" customHeight="1" s="19"/>
     <row r="343" ht="15.75" customHeight="1" s="19"/>
     <row r="344" ht="15.75" customHeight="1" s="19"/>
@@ -21420,7 +21702,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -21453,7 +21735,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22658,7 +22940,7 @@
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22784,7 +23066,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22816,7 +23098,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22847,7 +23129,7 @@
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -22974,7 +23256,7 @@
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -23005,7 +23287,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -2332,7 +2332,7 @@
       </c>
       <c r="N7" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O7" s="11" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #3 OK (medidor por equipo). #1/#2 NO: el disparo por lectura no está construido (pendiente §10.9). DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor).</t>
+          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #3 OK (medidor por equipo). #1/#2 NO: el disparo por lectura no está construido (pendiente §10.9). DECISIÓN TOMADA 12-09-2026 (Bryan): pme_activo_medidor pasa a NULL (BD/224). Con NULL, el medidor lo aporta cada equipo del plan (Plan_Mantenimiento_Activo.pac_activo_medidor, HU-083). Una programación, cuatro blowers. Falta el disparo por lectura (generador por medidor). || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>Desbloqueada el 12-09-2026 al existir hitos (HU-081). Generador hecho por Bryan (BD/222); falta el job nocturno que lo dispare con @SOLO_AUTOMATICAS=1.</t>
+          <t>Desbloqueada el 12-09-2026 al existir hitos (HU-081). Generador hecho por Bryan (BD/222); falta el job nocturno que lo dispare con @SOLO_AUTOMATICAS=1. || Cerrada el 22-09-2026: 4/4 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O9" s="11" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): 3 criterios OK (martes/jueves, último día del mes con bisiesto, último viernes). Base de datos y web terminadas. El último día del mes y el último viernes salen correctos, incluido febrero bisiesto.</t>
+          <t>Pruebas S3 (17-09): 3 criterios OK (martes/jueves, último día del mes con bisiesto, último viernes). Base de datos y web terminadas. El último día del mes y el último viernes salen correctos, incluido febrero bisiesto. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: UPS_REPUESTO_BODEGA_STOCK con las tres validaciones del CA1, editable desde la ficha del repuesto. Las alertas se ven en Existencias.aspx. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: UPS_REPUESTO_BODEGA_STOCK con las tres validaciones del CA1, editable desde la ficha del repuesto. Las alertas se ven en Existencias.aspx. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="N11" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O11" s="11" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: tipos 2 y 3 del mismo SP. El rechazo por saldo dice la existencia actual, y la devolucion reduce lo consumido de la orden. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: tipos 2 y 3 del mismo SP. El rechazo por saldo dice la existencia actual, y la devolucion reduce lo consumido de la orden. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: SEL/INS/UPD/DEL_REPUESTO (bloque 60), Repuestos.aspx y Repuesto.aspx, GET /repuestos en la API. Nace rep_controla_lote, que faltaba en el modelo. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: SEL/INS/UPD/DEL_REPUESTO (bloque 60), Repuestos.aspx y Repuesto.aspx, GET /repuestos en la API. Nace rep_controla_lote, que faltaba en el modelo. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="N13" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O13" s="11" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="P13" s="11" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: SEL_INVENTARIO_SALDO, Existencias.aspx y su ficha, GET /existencias. Sin cache, a proposito. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: SEL_INVENTARIO_SALDO, Existencias.aspx y su ficha, GET /existencias. Sin cache, a proposito. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): 3 criterios OK (ventana, feriado desplazado con fecha original, parada de planta). Base de datos y web terminadas. Hizo falta agregar pxc_desplaza para separar la parada de planta (no genera) del feriado (corre la fecha y guarda la original).</t>
+          <t>Pruebas S3 (17-09): 3 criterios OK (ventana, feriado desplazado con fecha original, parada de planta). Base de datos y web terminadas. Hizo falta agregar pxc_desplaza para separar la parada de planta (no genera) del feriado (corre la fecha y guarda la original). || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O15" s="11" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="P15" s="11" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: INS_INVENTARIO_MOVIMIENTO tipo 1, que exige el lote cuando el repuesto lo controla. POST /inventario-movimientos idempotente por uuid. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: INS_INVENTARIO_MOVIMIENTO tipo 1, que exige el lote cuando el repuesto lo controla. POST /inventario-movimientos idempotente por uuid. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O16" s="7" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>Construida por Bryan (bloque 91). Pruebas S3 (17-09): 2 criterios OK.</t>
+          <t>Construida por Bryan (bloque 91). Pruebas S3 (17-09): 2 criterios OK. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O17" s="11" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="P17" s="11" t="inlineStr">
         <is>
-          <t>Construida por Bryan (bloque 92). Pruebas S3 (17-09): #1 OK; #2 OK con la regla nueva del bloque 242 (consumo contra OT de un equipo no compatible exige el motivo).</t>
+          <t>Construida por Bryan (bloque 92). Pruebas S3 (17-09): #1 OK; #2 OK con la regla nueva del bloque 242 (consumo contra OT de un equipo no compatible exige el motivo). || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O18" s="7" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>Construida el 31-08-2026: SPs de Bodega y Bodega_Ubicacion (bloque 60), Bodegas.aspx y Bodega.aspx con las ubicaciones dentro, GET /bodegas y /bodegas/{id}/ubicaciones. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 31-08-2026: SPs de Bodega y Bodega_Ubicacion (bloque 60), Bodegas.aspx y Bodega.aspx con las ubicaciones dentro, GET /bodegas y /bodegas/{id}/ubicaciones. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="N19" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O19" s="11" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="P19" s="11" t="inlineStr">
         <is>
-          <t>Construida el 16-09-2026 (bloque 236 + RepuestoVidaUtil.aspx). Evidencia S3 con los 3 criterios OK. FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 16-09-2026 (bloque 236 + RepuestoVidaUtil.aspx). Evidencia S3 con los 3 criterios OK. FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O20" s="7" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): 2 criterios OK; la OT generada copia los pasos del procedimiento (bloque 241). Construida por Emilio Fuentes (01-09-2026). La BD ya estaba (bloque 101: SEL/INS/UPD/DEL_PROCEDIMIENTO y SEL_VARIABLE_MEDICION); revisada y confirmada. AGREGADO: datos de prueba (bloque 130), pantallas en Mantenimiento → Procedimientos (listado + ficha, patrón SigmaModal, ficha rediseñada estilo Programaciones) y permisos/menú (bloque 131). El código no es automático a propósito: la llave es (cliente, código, versión). Compila exitcode=0. PENDIENTE: prueba en navegador (verificación de criterios, de Catalina).</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK; la OT generada copia los pasos del procedimiento (bloque 241). Construida por Emilio Fuentes (01-09-2026). La BD ya estaba (bloque 101: SEL/INS/UPD/DEL_PROCEDIMIENTO y SEL_VARIABLE_MEDICION); revisada y confirmada. AGREGADO: datos de prueba (bloque 130), pantallas en Mantenimiento → Procedimientos (listado + ficha, patrón SigmaModal, ficha rediseñada estilo Programaciones) y permisos/menú (bloque 131). El código no es automático a propósito: la llave es (cliente, código, versión). Compila exitcode=0. PENDIENTE: prueba en navegador (verificación de criterios, de Catalina). || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="N21" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O21" s="11" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="P21" s="11" t="inlineStr">
         <is>
-          <t>Construida por Bryan (bloque 94). Pruebas S3 (17-09): #1 y #2 OK (el documento firmado es obligatorio para autorizar; la subida depende de la API de archivos del Sprint 6); #3 OK con la regla nueva del bloque 242 (tomar la OT con el permiso vencido se rechaza).</t>
+          <t>Construida por Bryan (bloque 94). Pruebas S3 (17-09): #1 y #2 OK (el documento firmado es obligatorio para autorizar; la subida depende de la API de archivos del Sprint 6); #3 OK con la regla nueva del bloque 242 (tomar la OT con el permiso vencido se rechaza). || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): 2 criterios OK sobre FNC_PROGRAMACION_FECHAS y la ficha. Base de datos y web terminadas. Los criterios se pueden ejercitar con la vista previa de fechas de la ficha.</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK sobre FNC_PROGRAMACION_FECHAS y la ficha. Base de datos y web terminadas. Los criterios se pueden ejercitar con la vista previa de fechas de la ficha. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N23" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O23" s="11" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="P23" s="11" t="inlineStr">
         <is>
-          <t>Pruebas S3 (17-09): 2 criterios OK. Base de datos y web terminadas. Hizo falta agregar pin_desde_ejecucion: sin esa columna los dos criterios de la historia se contradicen.</t>
+          <t>Pruebas S3 (17-09): 2 criterios OK. Base de datos y web terminadas. Hizo falta agregar pin_desde_ejecucion: sin esa columna los dos criterios de la historia se contradicen. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O24" s="7" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #1-#3 NO: las condiciones se definen pero el disparo al registrar la medición no está construido (pendiente §10.9). DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones.</t>
+          <t>Tomada por Bryan el 17-09-2026: disparo por lectura/medición construido (bloque 243) y los 3 criterios OK con evidencia. Pruebas S3 (17-09): #1-#3 NO: las condiciones se definen pero el disparo al registrar la medición no está construido (pendiente §10.9). DESBLOQUEADA 12-09-2026: HU-041 cerrada por Bryan (BD/224) y datos de prueba cargados (T-3261). El combo de variables ya tiene opciones. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="N25" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O25" s="11" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="P25" s="11" t="inlineStr">
         <is>
-          <t>· ALCANCE APP (30-08): Web → Web y App. Promovida a App: el bodeguero cuenta el inventario en el pasillo. Construida el 31-08-2026: tipos 4, 5, 6 y 8, con motivo obligatorio, y la familia del movimiento a la vista en el listado. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>· ALCANCE APP (30-08): Web → Web y App. Promovida a App: el bodeguero cuenta el inventario en el pasillo. Construida el 31-08-2026: tipos 4, 5, 6 y 8, con motivo obligatorio, y la familia del movimiento a la vista en el listado. Datos de prueba sembrados el 31-08 (bloque 64). FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O26" s="7" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P26" s="10" t="inlineStr">
         <is>
-          <t>Bryan (17-09-2026): el servidor exige la medición y respeta el punto de control al completar el paso (bloque 244); #2 y #3 OK por API. Pruebas S3 (17-09): #1 OK (bloque 241: un paso de OT por cada paso del procedimiento); #2 y #3 quedan definidos en la web y su exigencia al ejecutar es de la app (Sprint 6). Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil.</t>
+          <t>Bryan (17-09-2026): el servidor exige la medición y respeta el punto de control al completar el paso (bloque 244); #2 y #3 OK por API. Pruebas S3 (17-09): #1 OK (bloque 241: un paso de OT por cada paso del procedimiento); #2 y #3 quedan definidos en la web y su exigencia al ejecutar es de la app (Sprint 6). Construida por Emilio Fuentes (06-09-2026): BD (SEL/INS/UPD/DEL_PROCEDIMIENTO_PASO en BD/156, con orden unico por procedimiento, medicion que exige variable y baja logica que respeta ordenes) + Web (listado ProcedimientoPasos y ficha ProcedimientoPaso, con modelo/controller ProcedimientoPaso y VariableMedicion) + Menus (BD/157) + seguridad por cliente. Datos de prueba: los 10 pasos del procedimiento CAMBIO-MOTORREDUCTOR (BD/155). PENDIENTE (otra persona): pruebas por criterio, documentacion/Swagger y consumo movil. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="N27" s="9" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O27" s="11" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="P27" s="11" t="inlineStr">
         <is>
-          <t>Construida el 16-09-2026 (bloque 236 + ProveedorHistorial.aspx). Evidencia S3 con los 2 criterios OK. FALTA la verificacion de los criterios, que es de Catalina.</t>
+          <t>Construida el 16-09-2026 (bloque 236 + ProveedorHistorial.aspx). Evidencia S3 con los 2 criterios OK. FALTA la verificacion de los criterios, que es de Catalina. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O28" s="7" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>Construida por Bryan (bloque 97). Pruebas S3 (17-09): 2 criterios OK. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el prevencionista verifica el permiso en el frente de trabajo.</t>
+          <t>Construida por Bryan (bloque 97). Pruebas S3 (17-09): 2 criterios OK. · ALCANCE APP (30-08): Web → Web y App. Promovida a App: el prevencionista verifica el permiso en el frente de trabajo. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas. || Cerrada el 22-09-2026: 4/4 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O30" s="7" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O31" s="7" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas. || Cerrada el 22-09-2026: 3/3 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O32" s="7" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O33" s="7" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas.</t>
+          <t>Desarrollo construido y verificado contra la base. Cierra cuando esten sus pruebas. || Cerrada el 22-09-2026: 2/2 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Terminada</t>
         </is>
       </c>
       <c r="O34" s="7" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>Detectores de los otros modulos listos el 16-09-2026 (bloque 238): quedan las pruebas y documentacion de Catalina (T-3958/T-3959).</t>
+          <t>Detectores de los otros modulos listos el 16-09-2026 (bloque 238): quedan las pruebas y documentacion de Catalina (T-3958/T-3959). || Cerrada el 22-09-2026: 4/4 criterios web verificados con evidencia (SIGMA_Informe_Pruebas_Sprint_3.docx). La parte móvil se entrega en el Sprint 6.</t>
         </is>
       </c>
     </row>
@@ -6603,11 +6603,17 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="27" customHeight="1" s="19">
       <c r="A30" s="6" t="inlineStr">
@@ -7675,11 +7681,17 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="n"/>
-      <c r="J52" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="27" customHeight="1" s="19">
       <c r="A53" s="6" t="inlineStr">
@@ -8287,11 +8299,17 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="27" customHeight="1" s="19">
       <c r="A66" s="6" t="inlineStr">
@@ -8951,11 +8969,17 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27" customHeight="1" s="19">
       <c r="A80" s="6" t="inlineStr">
@@ -9521,11 +9545,17 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I91" s="6" t="n"/>
-      <c r="J91" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="41.25" customHeight="1" s="19">
       <c r="A92" s="6" t="inlineStr">
@@ -10041,11 +10071,17 @@
       </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="n"/>
-      <c r="J102" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="27" customHeight="1" s="19">
       <c r="A103" s="6" t="inlineStr">
@@ -10591,11 +10627,17 @@
       </c>
       <c r="H114" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="n"/>
-      <c r="J114" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="54.75" customHeight="1" s="19">
       <c r="A115" s="6" t="inlineStr">
@@ -11255,11 +11297,17 @@
       </c>
       <c r="H128" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I128" s="6" t="n"/>
-      <c r="J128" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="41.25" customHeight="1" s="19">
       <c r="A129" s="6" t="inlineStr">
@@ -11765,11 +11813,17 @@
       </c>
       <c r="H140" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I140" s="6" t="n"/>
-      <c r="J140" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="27" customHeight="1" s="19">
       <c r="A141" s="6" t="inlineStr">
@@ -12275,11 +12329,17 @@
       </c>
       <c r="H152" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I152" s="6" t="n"/>
-      <c r="J152" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="27" customHeight="1" s="19">
       <c r="A153" s="6" t="inlineStr">
@@ -12845,11 +12905,17 @@
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I164" s="6" t="n"/>
-      <c r="J164" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J164" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="41.25" customHeight="1" s="19">
       <c r="A165" s="6" t="inlineStr">
@@ -13223,11 +13289,17 @@
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I172" s="6" t="n"/>
-      <c r="J172" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="173" hidden="1" ht="27" customHeight="1" s="19">
       <c r="A173" s="6" t="inlineStr">
@@ -13541,13 +13613,15 @@
       </c>
       <c r="H179" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I179" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J179" s="7" t="inlineStr">
         <is>
-          <t>Procedimientos.aspx: listado con búsqueda, filtro de habilitados y botón Nuevo; marca "Global"/"Del cliente" y sin lápiz en los globales. Patrón nuevo SigmaModal.open. Compila exitcode=0; falta prueba en navegador.</t>
+          <t>Procedimientos.aspx: listado con búsqueda, filtro de habilitados y botón Nuevo; marca "Global"/"Del cliente" y sin lápiz en los globales. Patrón nuevo SigmaModal.open. Compila exitcode=0; falta prueba en navegador. || Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -13587,13 +13661,15 @@
       </c>
       <c r="H180" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I180" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
-          <t>Procedimiento.aspx: ficha RadWindow con clases sigma-modal-*; código y versión readonly al editar (son la llave), sección de permiso con combo condicional, validadores y Guardar/Cerrar. Rediseñada con el look de Programaciones (sigma-procedimiento.css). Compila; falta prueba en navegador.</t>
+          <t>Procedimiento.aspx: ficha RadWindow con clases sigma-modal-*; código y versión readonly al editar (son la llave), sección de permiso con combo condicional, validadores y Guardar/Cerrar. Rediseñada con el look de Programaciones (sigma-procedimiento.css). Compila; falta prueba en navegador. || Verificada en navegador el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -13679,13 +13755,15 @@
       </c>
       <c r="H182" s="6" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I182" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J182" s="7" t="inlineStr">
         <is>
-          <t>Permisos VER/CREAR EDITAR PROCEDIMIENTOS + Perfil_Permiso (bloque 131). Validación en servidor con Token.Puede/PuedeFuncion y filtro por cliente en el SP. Falta verificación en navegador.</t>
+          <t>Permisos VER/CREAR EDITAR PROCEDIMIENTOS + Perfil_Permiso (bloque 131). Validación en servidor con Token.Puede/PuedeFuncion y filtro por cliente en el SP. Falta verificación en navegador. || Permiso validado en el servidor y evidenciado el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
         </is>
       </c>
     </row>
@@ -13773,11 +13851,17 @@
       </c>
       <c r="H184" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I184" s="6" t="n"/>
-      <c r="J184" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="27" customHeight="1" s="19">
       <c r="A185" s="6" t="inlineStr">
@@ -14371,11 +14455,17 @@
       </c>
       <c r="H198" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I198" s="6" t="n"/>
-      <c r="J198" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="27" customHeight="1" s="19">
       <c r="A199" s="6" t="inlineStr">
@@ -14829,11 +14919,17 @@
       </c>
       <c r="H208" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I208" s="6" t="n"/>
-      <c r="J208" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="41.25" customHeight="1" s="19">
       <c r="A209" s="6" t="inlineStr">
@@ -15287,11 +15383,17 @@
       </c>
       <c r="H218" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I218" s="6" t="n"/>
-      <c r="J218" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I218" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J218" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="54.75" customHeight="1" s="19">
       <c r="A219" s="6" t="inlineStr">
@@ -15747,11 +15849,17 @@
       </c>
       <c r="H228" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I228" s="6" t="n"/>
-      <c r="J228" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I228" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J228" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="27" customHeight="1" s="19">
       <c r="A229" s="6" t="inlineStr">
@@ -16365,11 +16473,17 @@
       </c>
       <c r="H241" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I241" s="6" t="n"/>
-      <c r="J241" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I241" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J241" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="27" customHeight="1" s="19">
       <c r="A242" s="6" t="inlineStr">
@@ -16961,11 +17075,17 @@
       </c>
       <c r="H254" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I254" s="6" t="n"/>
-      <c r="J254" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I254" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="27" customHeight="1" s="19">
       <c r="A255" s="6" t="inlineStr">
@@ -17339,11 +17459,17 @@
       </c>
       <c r="H262" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I262" s="6" t="n"/>
-      <c r="J262" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I262" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="41.25" customHeight="1" s="19">
       <c r="A263" s="6" t="inlineStr">
@@ -17765,11 +17891,17 @@
       </c>
       <c r="H272" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I272" s="6" t="n"/>
-      <c r="J272" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I272" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J272" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="41.25" customHeight="1" s="19">
       <c r="A273" s="6" t="inlineStr">
@@ -18189,11 +18321,17 @@
       </c>
       <c r="H282" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I282" s="6" t="n"/>
-      <c r="J282" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I282" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J282" s="7" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="27" customHeight="1" s="19">
       <c r="A283" s="6" t="inlineStr">
@@ -18231,11 +18369,17 @@
       </c>
       <c r="H283" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I283" s="6" t="n"/>
-      <c r="J283" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I283" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J283" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="27" customHeight="1" s="19">
       <c r="A284" s="6" t="inlineStr">
@@ -18567,11 +18711,17 @@
       </c>
       <c r="H291" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I291" s="6" t="n"/>
-      <c r="J291" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" s="7" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="41.25" customHeight="1" s="19">
       <c r="A292" s="6" t="inlineStr">
@@ -18907,11 +19057,17 @@
       </c>
       <c r="H299" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I299" s="6" t="n"/>
-      <c r="J299" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" s="7" t="inlineStr">
+        <is>
+          <t>Casos escritos y ejecutados con evidencia el 22-09-2026 (SIGMA_Informe_Pruebas_Sprint_3.docx).</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="27" customHeight="1" s="19">
       <c r="A300" s="6" t="inlineStr">
@@ -19159,11 +19315,17 @@
       </c>
       <c r="H305" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I305" s="6" t="n"/>
-      <c r="J305" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I305" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J305" s="7" t="inlineStr">
+        <is>
+          <t>Carga desde planilla con fila buena, fila con código propio y fila mala: informe de errores verificado el 22-09-2026 (HU-068 #1).</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="27" customHeight="1" s="19">
       <c r="A306" s="6" t="inlineStr">
@@ -19327,11 +19489,17 @@
       </c>
       <c r="H309" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I309" s="6" t="n"/>
-      <c r="J309" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I309" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J309" s="7" t="inlineStr">
+        <is>
+          <t>Códigos escritos a mano y antiguos conservados tras editar (HU-069 #2, 22-09-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="27" customHeight="1" s="19">
       <c r="A310" s="6" t="inlineStr">
@@ -19931,11 +20099,17 @@
       </c>
       <c r="H323" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I323" s="6" t="n"/>
-      <c r="J323" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I323" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J323" s="7" t="inlineStr">
+        <is>
+          <t>Swagger (comentarios XML) y MD de estado al día el 22-09-2026.</t>
+        </is>
+      </c>
     </row>
     <row r="324" ht="41.25" customHeight="1" s="19">
       <c r="A324" s="6" t="inlineStr">
@@ -21522,7 +21696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10" customWidth="1" style="19" min="1" max="1"/>
@@ -21608,7 +21782,7 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sprint 6</t>
         </is>
       </c>
     </row>
@@ -21639,7 +21813,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sprint 6</t>
         </is>
       </c>
     </row>
@@ -21670,7 +21844,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sprint 6</t>
         </is>
       </c>
     </row>
@@ -21894,7 +22068,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -23418,24 +23592,569 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1" s="19"/>
-    <row r="65" ht="15.75" customHeight="1" s="19"/>
-    <row r="66" ht="15.75" customHeight="1" s="19"/>
-    <row r="67" ht="15.75" customHeight="1" s="19"/>
-    <row r="68" ht="15.75" customHeight="1" s="19"/>
-    <row r="69" ht="15.75" customHeight="1" s="19"/>
-    <row r="70" ht="15.75" customHeight="1" s="19"/>
-    <row r="71" ht="15.75" customHeight="1" s="19"/>
-    <row r="72" ht="15.75" customHeight="1" s="19"/>
-    <row r="73" ht="15.75" customHeight="1" s="19"/>
-    <row r="74" ht="15.75" customHeight="1" s="19"/>
-    <row r="75" ht="15.75" customHeight="1" s="19"/>
-    <row r="76" ht="15.75" customHeight="1" s="19"/>
-    <row r="77" ht="15.75" customHeight="1" s="19"/>
-    <row r="78" ht="15.75" customHeight="1" s="19"/>
-    <row r="79" ht="15.75" customHeight="1" s="19"/>
-    <row r="80" ht="15.75" customHeight="1" s="19"/>
-    <row r="81" ht="15.75" customHeight="1" s="19"/>
+    <row r="64" ht="39" customHeight="1" s="19">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>Ingreso con estante y lote</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>Dado que la bodega tiene ubicaciones
+Cuando registro un ingreso sin indicar en qué estante queda
+Entonces se rechaza; con estante y lote, la existencia queda en ese cubo (bodega, ubicación, lote)</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="39" customHeight="1" s="19">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>Existencias por estante y lote</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Cuando consulto las existencias
+Entonces veo la cantidad desglosada por bodega, ubicación y lote, y el umbral mínimo se evalúa por bodega</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="39" customHeight="1" s="19">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Reubicación dentro de la bodega</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>Cuando muevo un repuesto de un estante a otro de la misma bodega
+Entonces la existencia cambia de ubicación con un solo movimiento (sin salida ni entrada) y queda el historial de ubicaciones</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="39" customHeight="1" s="19">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>HU-059</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Saber en qué estante y de qué lote está cada repuesto</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Trazabilidad del lote</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>Cuando consulto un lote
+Entonces veo cuánto ingresó, cuánto se consumió y cuánto queda, con su vencimiento</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="39" customHeight="1" s="19">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>Etiquetas de una bodega</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>Cuando elijo una bodega en el centro de etiquetas e imprimo sus ubicaciones
+Entonces obtengo una hoja con una etiqueta por ubicación, cada una con su código y su QR</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="39" customHeight="1" s="19">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>Formato de papel</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>Cuando cambio el formato de papel
+Entonces la hoja se reacomoda al formato elegido y el código se lee completo, sin recortarse</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="39" customHeight="1" s="19">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>HU-066</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Identificar bodegas, ubicaciones y repuestos con etiquetas QR</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>Sin permiso</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>Dado que no tengo el permiso IMPRIMIR ETIQUETAS
+Cuando entro al centro de etiquetas
+Entonces no se me ofrece nada para imprimir</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="39" customHeight="1" s="19">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Consulta de una ubicación</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Cuando escaneo o escribo el código de una ubicación
+Entonces veo qué repuestos hay en ese estante, con cantidad y lote</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="39" customHeight="1" s="19">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Bodega y repuesto</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>Cuando el código es de una bodega o de un repuesto
+Entonces la misma pantalla muestra su desglose (por ubicación o por bodega)</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="39" customHeight="1" s="19">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>HU-067</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Consultar escaneando una etiqueta</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Código no reconocido</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Cuando el código no corresponde a nada del cliente
+Entonces se informa con claridad y no se muestra información de otro cliente</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="39" customHeight="1" s="19">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>HU-068</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Cargar y descargar el maestro de repuestos en planilla</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Carga desde la plantilla</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>Cuando descargo la plantilla, la completo y la cargo
+Entonces las filas válidas se crean; una fila mala no detiene el resto y se informa cuál falló y por qué</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="39" customHeight="1" s="19">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>HU-068</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Cargar y descargar el maestro de repuestos en planilla</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>Descarga a Excel</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>Cuando descargo a Excel desde el listado
+Entonces bajan los repuestos que coinciden con la búsqueda</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="39" customHeight="1" s="19">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>HU-069</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Generar los códigos automáticamente</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>Código generado</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Cuando creo un registro sin escribir el código
+Entonces el sistema lo genera con el prefijo de su módulo y el id (por ejemplo REP-44)</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="39" customHeight="1" s="19">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>HU-069</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Generar los códigos automáticamente</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>Códigos propios y antiguos</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>Dado un registro con código escrito a mano
+Cuando se guarda o se edita
+Entonces el código se conserva tal cual</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="39" customHeight="1" s="19">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>Quiebre de stock detectado</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>Dado un repuesto con existencia bajo el mínimo
+Cuando corre el detector de inventario
+Entonces se abre una alerta de stock mínimo con su severidad (sin existencia es crítica)</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="39" customHeight="1" s="19">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Sin duplicados y cierre automático</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Cuando el detector vuelve a correr sin cambios
+Entonces no duplica; cuando la existencia se repone
+Entonces la alerta se cierra sola como resuelta</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="39" customHeight="1" s="19">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Aviso en la web</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>Cuando hay alertas sin leer
+Entonces la campana muestra el contador y la bandeja las agrupa por categoría y gravedad</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="39" customHeight="1" s="19">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>HU-077</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Que el sistema avise lo que encuentra</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>La app recibe lo mismo</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Cuando la app consulta GET /alertas y /alertas/resumen
+Entonces recibe las mismas alertas y el mismo contador que la web</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+    </row>
     <row r="82" ht="15.75" customHeight="1" s="19"/>
     <row r="83" ht="15.75" customHeight="1" s="19"/>
     <row r="84" ht="15.75" customHeight="1" s="19"/>

--- a/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
+++ b/Fase 2/Sprint Backlogs/SIGMA_Sprint_Backlog_S3.xlsx
@@ -6651,11 +6651,17 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Validado con la Product Owner (registrado el 27-09-2026 por indicación de Bryan Chávez).</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="54.75" customHeight="1" s="19">
       <c r="A31" s="6" t="inlineStr">
@@ -7219,13 +7225,15 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Pendiente de la PO.</t>
+          <t>Pendiente de la PO. · Validado con la Product Owner (registrado el 27-09-2026 por indicación de Bryan Chávez).</t>
         </is>
       </c>
     </row>
@@ -7729,11 +7737,17 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>Validado con la Product Owner (registrado el 27-09-2026 por indicación de Bryan Chávez).</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="27" customHeight="1" s="19">
       <c r="A54" s="6" t="inlineStr">
@@ -18754,16 +18768,22 @@
       </c>
       <c r="G292" s="7" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I292" s="6" t="n"/>
-      <c r="J292" s="7" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I292" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J292" s="7" t="inlineStr">
+        <is>
+          <t>Reasignada de Catalina Pescio a Bryan Chávez el 27-09-2026. Medida en el PDF de impresión (lo que recibe la impresora) con modo impresión emulado: la prueba encontró que las hojas A4 salían de 68 × 36 y 97 × 56 mm en vez de 70 × 37 y 99 × 57 —los 8 mm de margen y 2 mm de separación no dejaban caber la plancha y se habían achicado las etiquetas—, así que no calzaban con el troquel. Corregido (sigma-impresion.css y @page en Etiquetas.aspx.cs: 3 × 8 sin margen, 2 × 5 con 6 mm, sin separación al imprimir). Tras el arreglo los tres formatos miden lo declarado (±1 mm). Evidencia: hu066_t3928_termica/a4-24/a4-10.pdf en Fase 2/Pruebas/capturas/S3. Queda por hacer la verificación con regla sobre papel, que requiere imprimir.</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="27" customHeight="1" s="19">
       <c r="A293" s="6" t="inlineStr">
